--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N73_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N73_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.82384606001518</v>
+        <v>9.396374984752466</v>
       </c>
       <c r="D2" t="n">
-        <v>59.06245874131713</v>
+        <v>9.597649545464034</v>
       </c>
       <c r="E2" t="n">
-        <v>16.27925123509997</v>
+        <v>2.645378325703744</v>
       </c>
       <c r="F2" t="n">
-        <v>19.5206980165537</v>
+        <v>3.172113427689976</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.23615344962698</v>
+        <v>4.425874935564384</v>
       </c>
       <c r="D3" t="n">
-        <v>26.13151348056854</v>
+        <v>4.246370940592388</v>
       </c>
       <c r="E3" t="n">
-        <v>16.27925123509997</v>
+        <v>2.645378325703744</v>
       </c>
       <c r="F3" t="n">
-        <v>19.5206980165537</v>
+        <v>3.172113427689976</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.52262174000305</v>
+        <v>8.859926032750495</v>
       </c>
       <c r="D4" t="n">
-        <v>50.39780547498054</v>
+        <v>8.189643389684338</v>
       </c>
       <c r="E4" t="n">
-        <v>16.27925123509997</v>
+        <v>2.645378325703744</v>
       </c>
       <c r="F4" t="n">
-        <v>19.5206980165537</v>
+        <v>3.172113427689976</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.33787462618393</v>
+        <v>4.767404626754889</v>
       </c>
       <c r="D5" t="n">
-        <v>5.011068993651132</v>
+        <v>0.814298711468309</v>
       </c>
       <c r="E5" t="n">
-        <v>16.27925123509997</v>
+        <v>2.645378325703744</v>
       </c>
       <c r="F5" t="n">
-        <v>19.5206980165537</v>
+        <v>3.172113427689976</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.96231358162315</v>
+        <v>2.106375957013762</v>
       </c>
       <c r="D6" t="n">
-        <v>17.78640362325012</v>
+        <v>2.890290588778145</v>
       </c>
       <c r="E6" t="n">
-        <v>16.27925123509997</v>
+        <v>2.645378325703744</v>
       </c>
       <c r="F6" t="n">
-        <v>19.5206980165537</v>
+        <v>3.172113427689976</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.15733068054941</v>
+        <v>5.06306623558928</v>
       </c>
       <c r="D7" t="n">
-        <v>5.209478840650986</v>
+        <v>0.8465403116057852</v>
       </c>
       <c r="E7" t="n">
-        <v>16.27925123509997</v>
+        <v>2.645378325703744</v>
       </c>
       <c r="F7" t="n">
-        <v>19.5206980165537</v>
+        <v>3.172113427689976</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.843238065435582</v>
+        <v>1.437026185633282</v>
       </c>
       <c r="D8" t="n">
-        <v>6.283404812635594</v>
+        <v>1.021053282053284</v>
       </c>
       <c r="E8" t="n">
-        <v>16.27925123509997</v>
+        <v>2.645378325703744</v>
       </c>
       <c r="F8" t="n">
-        <v>19.5206980165537</v>
+        <v>3.172113427689976</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.22455056130246</v>
+        <v>7.023989466211651</v>
       </c>
       <c r="D9" t="n">
-        <v>12.04440459868687</v>
+        <v>1.957215747286616</v>
       </c>
       <c r="E9" t="n">
-        <v>16.27925123509997</v>
+        <v>2.645378325703744</v>
       </c>
       <c r="F9" t="n">
-        <v>19.5206980165537</v>
+        <v>3.172113427689976</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>53.2142008223455</v>
+        <v>8.647307633631144</v>
       </c>
       <c r="D10" t="n">
-        <v>45.65206342316488</v>
+        <v>7.418460306264293</v>
       </c>
       <c r="E10" t="n">
-        <v>16.27925123509997</v>
+        <v>2.645378325703744</v>
       </c>
       <c r="F10" t="n">
-        <v>19.5206980165537</v>
+        <v>3.172113427689976</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>44.37323175467046</v>
+        <v>7.210650160133951</v>
       </c>
       <c r="D11" t="n">
-        <v>40.80750763293793</v>
+        <v>6.631219990352415</v>
       </c>
       <c r="E11" t="n">
-        <v>16.27925123509997</v>
+        <v>2.645378325703744</v>
       </c>
       <c r="F11" t="n">
-        <v>19.5206980165537</v>
+        <v>3.172113427689976</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
